--- a/artfynd/A 31839-2022 artfynd.xlsx
+++ b/artfynd/A 31839-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31839-2022 artfynd.xlsx
+++ b/artfynd/A 31839-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103998239</v>
+        <v>103998416</v>
       </c>
       <c r="B2" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>492</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545925.9961037355</v>
+        <v>545949</v>
       </c>
       <c r="R2" t="n">
-        <v>7009796.817637669</v>
+        <v>7009808</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103998218</v>
+        <v>103998355</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545922.1431066971</v>
+        <v>546007</v>
       </c>
       <c r="R3" t="n">
-        <v>7009781.875795874</v>
+        <v>7009840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,37 +907,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103998250</v>
+        <v>103998337</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545919.0673674798</v>
+        <v>545930</v>
       </c>
       <c r="R4" t="n">
-        <v>7009807.545900809</v>
+        <v>7009901</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,37 +1023,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103998416</v>
+        <v>103998216</v>
       </c>
       <c r="B5" t="n">
-        <v>73685</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>492</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545948.8759241471</v>
+        <v>545919</v>
       </c>
       <c r="R5" t="n">
-        <v>7009807.970231356</v>
+        <v>7009813</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,55 +1139,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103998294</v>
+        <v>103998342</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>revir, ej häckning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Källmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545910.9386316505</v>
+        <v>545982</v>
       </c>
       <c r="R6" t="n">
-        <v>7009902.614904161</v>
+        <v>7009829</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1219,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,37 +1255,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103998355</v>
+        <v>103998318</v>
       </c>
       <c r="B7" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546007.5976592547</v>
+        <v>545924</v>
       </c>
       <c r="R7" t="n">
-        <v>7009839.934017257</v>
+        <v>7009764</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,15 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103998318</v>
+        <v>103998239</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6439</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1446,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545924.6581137746</v>
+        <v>545926</v>
       </c>
       <c r="R8" t="n">
-        <v>7009763.866641461</v>
+        <v>7009797</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,15 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103998216</v>
+        <v>103998292</v>
       </c>
       <c r="B9" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,21 +1498,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>6439</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1567,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545918.996765345</v>
+        <v>545957</v>
       </c>
       <c r="R9" t="n">
-        <v>7009812.507199436</v>
+        <v>7009802</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1612,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,37 +1603,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103998266</v>
+        <v>103998396</v>
       </c>
       <c r="B10" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219795</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1688,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545911.8667197556</v>
+        <v>545901</v>
       </c>
       <c r="R10" t="n">
-        <v>7009805.63896375</v>
+        <v>7009798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1723,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1733,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,50 +1719,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103998292</v>
+        <v>103998294</v>
       </c>
       <c r="B11" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>revir, ej häckning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Källmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545957.0890379362</v>
+        <v>545911</v>
       </c>
       <c r="R11" t="n">
-        <v>7009802.222643663</v>
+        <v>7009902</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1804,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,37 +1840,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103998358</v>
+        <v>103998266</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>219795</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1930,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545931.0669339503</v>
+        <v>545912</v>
       </c>
       <c r="R12" t="n">
-        <v>7009789.671879097</v>
+        <v>7009805</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,7 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2011,37 +1956,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103998396</v>
+        <v>103998250</v>
       </c>
       <c r="B13" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2051,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545901.142723094</v>
+        <v>545919</v>
       </c>
       <c r="R13" t="n">
-        <v>7009797.366244136</v>
+        <v>7009808</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2086,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2096,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2125,248 +2065,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>103998342</v>
-      </c>
-      <c r="B14" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>4769</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Svavelriska</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Lactarius scrobiculatus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Källmyran, Jmt</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>545981.5439154443</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7009829.638105797</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>103998337</v>
-      </c>
-      <c r="B15" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Källmyran, Jmt</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>545929.9392541705</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7009900.629783235</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 31839-2022 artfynd.xlsx
+++ b/artfynd/A 31839-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998416</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998355</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998337</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998216</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998342</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998318</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998239</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998292</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998396</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1837,6 +1887,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998294</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1953,6 +2008,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998266</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2069,8 +2129,27 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998250</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>